--- a/htr-ML-Sections/ig/StructureDefinition-fr-lm-participant.xlsx
+++ b/htr-ML-Sections/ig/StructureDefinition-fr-lm-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T12:47:35+00:00</t>
+    <t>2026-05-07T13:30:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-ML-Sections/ig/StructureDefinition-fr-lm-participant.xlsx
+++ b/htr-ML-Sections/ig/StructureDefinition-fr-lm-participant.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="109">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T13:30:39+00:00</t>
+    <t>2026-05-12T13:21:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -250,7 +250,27 @@
     <t>Base</t>
   </si>
   <si>
-    <t>fr-lm-participant.typeParticipation</t>
+    <t>fr-lm-participant.identifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier
+</t>
+  </si>
+  <si>
+    <t>Identifiants de la personne</t>
+  </si>
+  <si>
+    <t>fr-lm-participant.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-human-name
+</t>
+  </si>
+  <si>
+    <t>Nom de la personne</t>
+  </si>
+  <si>
+    <t>fr-lm-participant.type</t>
   </si>
   <si>
     <t>1</t>
@@ -258,48 +278,6 @@
   <si>
     <t xml:space="preserve">CodeableConcept
 </t>
-  </si>
-  <si>
-    <t>Type de participation.</t>
-  </si>
-  <si>
-    <t>fr-lm-participant.roleFonctionnel</t>
-  </si>
-  <si>
-    <t>Rôle fonctionnel.</t>
-  </si>
-  <si>
-    <t>fr-lm-participant.dateDebutEtOuFinParticipation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dateTime
-</t>
-  </si>
-  <si>
-    <t>Date de début et/ou de fin de la participation.</t>
-  </si>
-  <si>
-    <t>fr-lm-participant.identifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifier
-</t>
-  </si>
-  <si>
-    <t>Identifiants de la personne</t>
-  </si>
-  <si>
-    <t>fr-lm-participant.name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-human-name
-</t>
-  </si>
-  <si>
-    <t>Nom de la personne</t>
-  </si>
-  <si>
-    <t>fr-lm-participant.type</t>
   </si>
   <si>
     <t>Type de participation</t>
@@ -672,7 +650,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ14"/>
+  <dimension ref="A1:AJ11"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="41.8671875" customWidth="true" bestFit="true"/>
@@ -935,28 +913,28 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G3" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J3" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K3" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="G3" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H3" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J3" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="L3" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="M3" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1010,10 +988,10 @@
         <v>78</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>73</v>
@@ -1024,10 +1002,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1038,7 +1016,7 @@
         <v>74</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>73</v>
@@ -1050,7 +1028,7 @@
         <v>73</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="L4" t="s" s="2">
         <v>83</v>
@@ -1107,13 +1085,13 @@
         <v>73</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>73</v>
@@ -1135,10 +1113,10 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>73</v>
@@ -1150,13 +1128,13 @@
         <v>73</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1186,10 +1164,10 @@
         <v>73</v>
       </c>
       <c r="Y5" t="s" s="2">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="Z5" t="s" s="2">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="AA5" t="s" s="2">
         <v>73</v>
@@ -1210,10 +1188,10 @@
         <v>84</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>73</v>
@@ -1224,10 +1202,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1238,7 +1216,7 @@
         <v>74</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>73</v>
@@ -1250,13 +1228,13 @@
         <v>73</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1286,10 +1264,10 @@
         <v>73</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>73</v>
@@ -1307,13 +1285,13 @@
         <v>73</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>73</v>
@@ -1324,10 +1302,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1338,7 +1316,7 @@
         <v>74</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>73</v>
@@ -1350,13 +1328,13 @@
         <v>73</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1407,13 +1385,13 @@
         <v>73</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>73</v>
@@ -1424,10 +1402,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1435,10 +1413,10 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>73</v>
@@ -1450,13 +1428,13 @@
         <v>73</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1486,10 +1464,10 @@
         <v>73</v>
       </c>
       <c r="Y8" t="s" s="2">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="Z8" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="AA8" t="s" s="2">
         <v>73</v>
@@ -1507,13 +1485,13 @@
         <v>73</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>73</v>
@@ -1524,10 +1502,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1538,7 +1516,7 @@
         <v>74</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>73</v>
@@ -1550,13 +1528,13 @@
         <v>73</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1586,34 +1564,34 @@
         <v>73</v>
       </c>
       <c r="Y9" t="s" s="2">
-        <v>99</v>
+        <v>73</v>
       </c>
       <c r="Z9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF9" t="s" s="2">
         <v>100</v>
-      </c>
-      <c r="AA9" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB9" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD9" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE9" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF9" t="s" s="2">
-        <v>97</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>73</v>
@@ -1624,10 +1602,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1638,7 +1616,7 @@
         <v>74</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>73</v>
@@ -1650,13 +1628,13 @@
         <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1707,13 +1685,13 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>73</v>
@@ -1724,10 +1702,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1735,10 +1713,10 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>73</v>
@@ -1750,13 +1728,13 @@
         <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1807,318 +1785,18 @@
         <v>73</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E12" s="2"/>
-      <c r="F12" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G12" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K12" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="L12" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
-      <c r="P12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q12" s="2"/>
-      <c r="R12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF12" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AG12" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH12" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ12" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="D13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E13" s="2"/>
-      <c r="F13" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K13" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L13" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
-      <c r="P13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q13" s="2"/>
-      <c r="R13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="AG13" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ13" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="C14" s="2"/>
-      <c r="D14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E14" s="2"/>
-      <c r="F14" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G14" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K14" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="L14" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
-      <c r="P14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q14" s="2"/>
-      <c r="R14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="AG14" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH14" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ14" t="s" s="2">
         <v>73</v>
       </c>
     </row>
